--- a/lpo_df.xlsx
+++ b/lpo_df.xlsx
@@ -429,7 +429,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:T7"/>
+  <dimension ref="A1:T2"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -534,10 +534,10 @@
         <v>0</v>
       </c>
       <c r="B2" t="n">
-        <v>7638551</v>
+        <v>7686779</v>
       </c>
       <c r="C2" s="2" t="n">
-        <v>45406.69809027778</v>
+        <v>45580.66552083333</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>
@@ -551,18 +551,18 @@
       </c>
       <c r="F2" t="inlineStr">
         <is>
-          <t>24001844</t>
+          <t>24004829</t>
         </is>
       </c>
       <c r="G2" t="inlineStr"/>
       <c r="H2" t="inlineStr">
         <is>
-          <t>Kobian Kenya Ltd</t>
+          <t>Jalaram Industrial Supplies Ltd</t>
         </is>
       </c>
       <c r="I2" t="inlineStr">
         <is>
-          <t>Nairobi - KES</t>
+          <t>Mombasa</t>
         </is>
       </c>
       <c r="J2" t="inlineStr">
@@ -580,22 +580,22 @@
       </c>
       <c r="M2" t="inlineStr">
         <is>
-          <t>OTLCC0001054</t>
+          <t>OTMCT0003025</t>
         </is>
       </c>
       <c r="N2" t="inlineStr">
         <is>
-          <t>Petroleum Ether AR</t>
+          <t>Silicon Tube - Black</t>
         </is>
       </c>
       <c r="O2" t="n">
-        <v>1380</v>
+        <v>170</v>
       </c>
       <c r="P2" t="n">
-        <v>5</v>
+        <v>60</v>
       </c>
       <c r="Q2" t="n">
-        <v>6900</v>
+        <v>10200</v>
       </c>
       <c r="R2" t="inlineStr"/>
       <c r="S2" t="inlineStr">
@@ -604,406 +604,6 @@
         </is>
       </c>
       <c r="T2" t="inlineStr">
-        <is>
-          <t>CLOSED</t>
-        </is>
-      </c>
-    </row>
-    <row r="3">
-      <c r="A3" s="1" t="n">
-        <v>1</v>
-      </c>
-      <c r="B3" t="n">
-        <v>7638551</v>
-      </c>
-      <c r="C3" s="2" t="n">
-        <v>45406.69809027778</v>
-      </c>
-      <c r="D3" t="inlineStr">
-        <is>
-          <t>STANDARD</t>
-        </is>
-      </c>
-      <c r="E3" t="inlineStr">
-        <is>
-          <t>APPROVED</t>
-        </is>
-      </c>
-      <c r="F3" t="inlineStr">
-        <is>
-          <t>24001844</t>
-        </is>
-      </c>
-      <c r="G3" t="inlineStr"/>
-      <c r="H3" t="inlineStr">
-        <is>
-          <t>Kobian Kenya Ltd</t>
-        </is>
-      </c>
-      <c r="I3" t="inlineStr">
-        <is>
-          <t>Nairobi - KES</t>
-        </is>
-      </c>
-      <c r="J3" t="inlineStr">
-        <is>
-          <t>Edibles</t>
-        </is>
-      </c>
-      <c r="K3" t="inlineStr">
-        <is>
-          <t>Edibles</t>
-        </is>
-      </c>
-      <c r="L3" t="n">
-        <v>3</v>
-      </c>
-      <c r="M3" t="inlineStr">
-        <is>
-          <t>OTLCI0007406</t>
-        </is>
-      </c>
-      <c r="N3" t="inlineStr">
-        <is>
-          <t>Isooctane</t>
-        </is>
-      </c>
-      <c r="O3" t="n">
-        <v>2400</v>
-      </c>
-      <c r="P3" t="n">
-        <v>5</v>
-      </c>
-      <c r="Q3" t="n">
-        <v>12000</v>
-      </c>
-      <c r="R3" t="inlineStr"/>
-      <c r="S3" t="inlineStr">
-        <is>
-          <t>Adisa, Miss Lynda</t>
-        </is>
-      </c>
-      <c r="T3" t="inlineStr">
-        <is>
-          <t>CLOSED</t>
-        </is>
-      </c>
-    </row>
-    <row r="4">
-      <c r="A4" s="1" t="n">
-        <v>2</v>
-      </c>
-      <c r="B4" t="n">
-        <v>7638551</v>
-      </c>
-      <c r="C4" s="2" t="n">
-        <v>45406.69809027778</v>
-      </c>
-      <c r="D4" t="inlineStr">
-        <is>
-          <t>STANDARD</t>
-        </is>
-      </c>
-      <c r="E4" t="inlineStr">
-        <is>
-          <t>APPROVED</t>
-        </is>
-      </c>
-      <c r="F4" t="inlineStr">
-        <is>
-          <t>24001844</t>
-        </is>
-      </c>
-      <c r="G4" t="inlineStr"/>
-      <c r="H4" t="inlineStr">
-        <is>
-          <t>Kobian Kenya Ltd</t>
-        </is>
-      </c>
-      <c r="I4" t="inlineStr">
-        <is>
-          <t>Nairobi - KES</t>
-        </is>
-      </c>
-      <c r="J4" t="inlineStr">
-        <is>
-          <t>Edibles</t>
-        </is>
-      </c>
-      <c r="K4" t="inlineStr">
-        <is>
-          <t>Edibles</t>
-        </is>
-      </c>
-      <c r="L4" t="n">
-        <v>2</v>
-      </c>
-      <c r="M4" t="inlineStr">
-        <is>
-          <t>OTLCA0003899</t>
-        </is>
-      </c>
-      <c r="N4" t="inlineStr">
-        <is>
-          <t>Acetic Acid AR -(Monhydrous/Anhydrous)</t>
-        </is>
-      </c>
-      <c r="O4" t="n">
-        <v>840</v>
-      </c>
-      <c r="P4" t="n">
-        <v>5</v>
-      </c>
-      <c r="Q4" t="n">
-        <v>4200</v>
-      </c>
-      <c r="R4" t="inlineStr"/>
-      <c r="S4" t="inlineStr">
-        <is>
-          <t>Adisa, Miss Lynda</t>
-        </is>
-      </c>
-      <c r="T4" t="inlineStr">
-        <is>
-          <t>CLOSED</t>
-        </is>
-      </c>
-    </row>
-    <row r="5">
-      <c r="A5" s="1" t="n">
-        <v>3</v>
-      </c>
-      <c r="B5" t="n">
-        <v>7638551</v>
-      </c>
-      <c r="C5" s="2" t="n">
-        <v>45406.69809027778</v>
-      </c>
-      <c r="D5" t="inlineStr">
-        <is>
-          <t>STANDARD</t>
-        </is>
-      </c>
-      <c r="E5" t="inlineStr">
-        <is>
-          <t>APPROVED</t>
-        </is>
-      </c>
-      <c r="F5" t="inlineStr">
-        <is>
-          <t>24001844</t>
-        </is>
-      </c>
-      <c r="G5" t="inlineStr"/>
-      <c r="H5" t="inlineStr">
-        <is>
-          <t>Kobian Kenya Ltd</t>
-        </is>
-      </c>
-      <c r="I5" t="inlineStr">
-        <is>
-          <t>Nairobi - KES</t>
-        </is>
-      </c>
-      <c r="J5" t="inlineStr">
-        <is>
-          <t>Edibles</t>
-        </is>
-      </c>
-      <c r="K5" t="inlineStr">
-        <is>
-          <t>Edibles</t>
-        </is>
-      </c>
-      <c r="L5" t="n">
-        <v>5</v>
-      </c>
-      <c r="M5" t="inlineStr">
-        <is>
-          <t>OTLCH0009016</t>
-        </is>
-      </c>
-      <c r="N5" t="inlineStr">
-        <is>
-          <t>Hydrochloric Acid Conc</t>
-        </is>
-      </c>
-      <c r="O5" t="n">
-        <v>520</v>
-      </c>
-      <c r="P5" t="n">
-        <v>2.5</v>
-      </c>
-      <c r="Q5" t="n">
-        <v>1300</v>
-      </c>
-      <c r="R5" t="inlineStr"/>
-      <c r="S5" t="inlineStr">
-        <is>
-          <t>Adisa, Miss Lynda</t>
-        </is>
-      </c>
-      <c r="T5" t="inlineStr">
-        <is>
-          <t>CLOSED</t>
-        </is>
-      </c>
-    </row>
-    <row r="6">
-      <c r="A6" s="1" t="n">
-        <v>4</v>
-      </c>
-      <c r="B6" t="n">
-        <v>7638551</v>
-      </c>
-      <c r="C6" s="2" t="n">
-        <v>45406.69809027778</v>
-      </c>
-      <c r="D6" t="inlineStr">
-        <is>
-          <t>STANDARD</t>
-        </is>
-      </c>
-      <c r="E6" t="inlineStr">
-        <is>
-          <t>APPROVED</t>
-        </is>
-      </c>
-      <c r="F6" t="inlineStr">
-        <is>
-          <t>24001844</t>
-        </is>
-      </c>
-      <c r="G6" t="inlineStr"/>
-      <c r="H6" t="inlineStr">
-        <is>
-          <t>Kobian Kenya Ltd</t>
-        </is>
-      </c>
-      <c r="I6" t="inlineStr">
-        <is>
-          <t>Nairobi - KES</t>
-        </is>
-      </c>
-      <c r="J6" t="inlineStr">
-        <is>
-          <t>Edibles</t>
-        </is>
-      </c>
-      <c r="K6" t="inlineStr">
-        <is>
-          <t>Edibles</t>
-        </is>
-      </c>
-      <c r="L6" t="n">
-        <v>6</v>
-      </c>
-      <c r="M6" t="inlineStr">
-        <is>
-          <t>OTLCS0009032</t>
-        </is>
-      </c>
-      <c r="N6" t="inlineStr">
-        <is>
-          <t>Sulphuric Acid Conc</t>
-        </is>
-      </c>
-      <c r="O6" t="n">
-        <v>720</v>
-      </c>
-      <c r="P6" t="n">
-        <v>2.5</v>
-      </c>
-      <c r="Q6" t="n">
-        <v>1800</v>
-      </c>
-      <c r="R6" t="inlineStr"/>
-      <c r="S6" t="inlineStr">
-        <is>
-          <t>Adisa, Miss Lynda</t>
-        </is>
-      </c>
-      <c r="T6" t="inlineStr">
-        <is>
-          <t>CLOSED</t>
-        </is>
-      </c>
-    </row>
-    <row r="7">
-      <c r="A7" s="1" t="n">
-        <v>5</v>
-      </c>
-      <c r="B7" t="n">
-        <v>7638551</v>
-      </c>
-      <c r="C7" s="2" t="n">
-        <v>45406.69809027778</v>
-      </c>
-      <c r="D7" t="inlineStr">
-        <is>
-          <t>STANDARD</t>
-        </is>
-      </c>
-      <c r="E7" t="inlineStr">
-        <is>
-          <t>APPROVED</t>
-        </is>
-      </c>
-      <c r="F7" t="inlineStr">
-        <is>
-          <t>24001844</t>
-        </is>
-      </c>
-      <c r="G7" t="inlineStr"/>
-      <c r="H7" t="inlineStr">
-        <is>
-          <t>Kobian Kenya Ltd</t>
-        </is>
-      </c>
-      <c r="I7" t="inlineStr">
-        <is>
-          <t>Nairobi - KES</t>
-        </is>
-      </c>
-      <c r="J7" t="inlineStr">
-        <is>
-          <t>Edibles</t>
-        </is>
-      </c>
-      <c r="K7" t="inlineStr">
-        <is>
-          <t>Edibles</t>
-        </is>
-      </c>
-      <c r="L7" t="n">
-        <v>4</v>
-      </c>
-      <c r="M7" t="inlineStr">
-        <is>
-          <t>OTLCA0008998</t>
-        </is>
-      </c>
-      <c r="N7" t="inlineStr">
-        <is>
-          <t>Acetone</t>
-        </is>
-      </c>
-      <c r="O7" t="n">
-        <v>960</v>
-      </c>
-      <c r="P7" t="n">
-        <v>5</v>
-      </c>
-      <c r="Q7" t="n">
-        <v>4800</v>
-      </c>
-      <c r="R7" t="inlineStr"/>
-      <c r="S7" t="inlineStr">
-        <is>
-          <t>Adisa, Miss Lynda</t>
-        </is>
-      </c>
-      <c r="T7" t="inlineStr">
         <is>
           <t>CLOSED</t>
         </is>
